--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_276_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_276_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1128</v>
+        <v>2.5204</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0891</v>
+        <v>1.8663</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0237</v>
+        <v>0.6541</v>
       </c>
       <c r="G2" t="n">
         <v>1.7277</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3129</v>
+        <v>0.7205</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2571</v>
+        <v>1.0343</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0558</v>
+        <v>-0.3139</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2479</v>
+        <v>1.2031</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4599</v>
+        <v>-1.0209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7879</v>
+        <v>2.2241</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2336</v>
+        <v>-0.9415</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.879</v>
+        <v>-0.7841</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3546</v>
+        <v>-0.1574</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7789</v>
+        <v>-0.9625</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4782</v>
+        <v>-0.6009</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6993</v>
+        <v>-0.3616</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4547</v>
+        <v>0.021</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4008</v>
+        <v>-0.1833</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0539</v>
+        <v>0.2042</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0897</v>
+        <v>-0.1748</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2388</v>
+        <v>-0.0584</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8509</v>
+        <v>-0.1164</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.903</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4367</v>
+        <v>0.2755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4662</v>
+        <v>0.5335</v>
       </c>
       <c r="G4" t="n">
         <v>0.4039</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3188</v>
+        <v>1.2248</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4525</v>
+        <v>0.2912</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8663</v>
+        <v>0.9335</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8197</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1103</v>
+        <v>0.5323</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5171</v>
+        <v>-0.5511</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4068</v>
+        <v>1.0834</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.0222</v>
+        <v>-0.5392</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3926</v>
+        <v>0.7692</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6296</v>
+        <v>-1.3084</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.5071</v>
+        <v>0.6868</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.0413</v>
+        <v>0.8878</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4658</v>
+        <v>-0.201</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5151</v>
+        <v>-1.226</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3513</v>
+        <v>-0.1186</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1638</v>
+        <v>-1.1074</v>
       </c>
       <c r="P5" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.0876</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.3195</v>
-      </c>
       <c r="S5" t="n">
-        <v>2.0383</v>
+        <v>0.3756</v>
       </c>
       <c r="T5" t="n">
-        <v>2.222</v>
+        <v>0.1537</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1836</v>
+        <v>0.2219</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6647999999999999</v>
+        <v>0.2109</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8216</v>
+        <v>-0.409</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1569</v>
+        <v>0.6199</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9415</v>
+        <v>-2.2336</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7841</v>
+        <v>-1.879</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1574</v>
+        <v>-0.3546</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9625</v>
+        <v>-0.7789</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6009</v>
+        <v>-1.4782</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3616</v>
+        <v>0.6993</v>
       </c>
       <c r="M6" t="n">
-        <v>0.021</v>
+        <v>-1.4547</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1833</v>
+        <v>-0.4008</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2042</v>
+        <v>-1.0539</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0427</v>
+        <v>1.0528</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.8591</v>
+        <v>0.3699</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1836</v>
+        <v>0.6829</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0997</v>
+        <v>-1.2658</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1159</v>
+        <v>-1.7398</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0162</v>
+        <v>0.474</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5392</v>
+        <v>-3.0222</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7692</v>
+        <v>-1.3926</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3084</v>
+        <v>-1.6296</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6868</v>
+        <v>-2.5071</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8878</v>
+        <v>-1.0413</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.201</v>
+        <v>-1.4658</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.226</v>
+        <v>-0.5151</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1186</v>
+        <v>-0.3513</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1074</v>
+        <v>-0.1638</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2564</v>
+        <v>0.8828</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.411</v>
+        <v>0.9992</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1546</v>
+        <v>-0.1164</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.123</v>
+        <v>-1.9715</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8517</v>
+        <v>-0.7337</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2714</v>
+        <v>-1.2377</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9961</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.127</v>
+        <v>0.0246</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1554</v>
+        <v>-3.6197</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8934</v>
+        <v>-0.8156</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2621</v>
+        <v>-2.8041</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7805</v>
+        <v>-2.0527</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3421</v>
+        <v>0.2895</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4384</v>
+        <v>-2.3422</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9516</v>
+        <v>-0.7765</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3592</v>
+        <v>0.7226</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5924</v>
+        <v>-1.4991</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1711</v>
+        <v>-1.2762</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0171</v>
+        <v>-0.4331</v>
       </c>
       <c r="O9" t="n">
-        <v>0.154</v>
+        <v>-0.8431</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5373</v>
+        <v>-0.1907</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6097</v>
+        <v>-0.0391</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.147</v>
+        <v>-0.1516</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3349</v>
+        <v>-3.8962</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.598</v>
+        <v>-2.9366</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7369</v>
+        <v>-0.9596</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0527</v>
+        <v>-0.7805</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2895</v>
+        <v>-0.3421</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3422</v>
+        <v>-0.4384</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7765</v>
+        <v>-0.9516</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7226</v>
+        <v>-0.3592</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4991</v>
+        <v>-0.5924</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2762</v>
+        <v>0.1711</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4331</v>
+        <v>0.0171</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8431</v>
+        <v>0.154</v>
       </c>
       <c r="P10" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9058</v>
+        <v>-0.2781</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>0.5665</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0843</v>
+        <v>-0.8445</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6083</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6083</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2244</v>
+        <v>-5.477499999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.812</v>
+        <v>-6.0649</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5872999999999999</v>
+        <v>0.5875999999999997</v>
       </c>
       <c r="G11" t="n">
         <v>-9.434200000000001</v>
@@ -1288,7 +1288,7 @@
         <v>-3.0703</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5612000000000003</v>
+        <v>0.5612000000000004</v>
       </c>
       <c r="L11" t="n">
         <v>-3.6315</v>
@@ -1300,10 +1300,10 @@
         <v>-1.8645</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.4995</v>
+        <v>-4.499499999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>4.6391</v>
+        <v>4.639100000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-6.9586</v>
@@ -1312,16 +1312,16 @@
         <v>11.5976</v>
       </c>
       <c r="S11" t="n">
-        <v>2.890499999999999</v>
+        <v>3.6375</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5391</v>
+        <v>3.2859</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3515</v>
+        <v>0.3514999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-4.3199</v>
+        <v>-4.319900000000001</v>
       </c>
       <c r="W11" t="n">
         <v>0.6778999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.1492</v>
+        <v>5.0877</v>
       </c>
       <c r="E12" t="n">
-        <v>3.7915</v>
+        <v>3.6736</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3577</v>
+        <v>1.4141</v>
       </c>
       <c r="G12" t="n">
         <v>4.4825</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1735</v>
+        <v>-0.235</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2131</v>
+        <v>-0.1566</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1786</v>
+        <v>3.6054</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1093</v>
+        <v>2.3452</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0693</v>
+        <v>1.2602</v>
       </c>
       <c r="G13" t="n">
         <v>2.5612</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6146</v>
+        <v>-0.1878</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2412</v>
+        <v>-0.0503</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6886</v>
+        <v>2.5072</v>
       </c>
       <c r="E14" t="n">
-        <v>3.084</v>
+        <v>1.4375</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3953</v>
+        <v>1.0697</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3607</v>
+        <v>-0.7184</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3038</v>
+        <v>-0.2365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0569</v>
+        <v>-0.4819</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3224</v>
+        <v>-1.1792</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8942</v>
+        <v>-0.3894</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4282</v>
+        <v>-0.7899</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9617</v>
+        <v>0.4608</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5904</v>
+        <v>0.1528</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3713</v>
+        <v>0.308</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0058</v>
+        <v>-0.2203</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7616</v>
+        <v>0.3306</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2443</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1418</v>
+        <v>2.2862</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2554</v>
+        <v>2.3898</v>
       </c>
       <c r="E15" t="n">
         <v>0.9806</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2747</v>
+        <v>1.4091</v>
       </c>
       <c r="G15" t="n">
         <v>1.8799</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9287</v>
+        <v>-0.7943</v>
       </c>
       <c r="T15" t="n">
         <v>-0.8962</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0325</v>
+        <v>0.1019</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0291</v>
+        <v>1.4926</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8478</v>
+        <v>2.0224</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1813</v>
+        <v>-0.5298</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7184</v>
+        <v>0.3607</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2365</v>
+        <v>0.3038</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4819</v>
+        <v>0.0569</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1792</v>
+        <v>1.3224</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3894</v>
+        <v>0.8942</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7899</v>
+        <v>0.4282</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4608</v>
+        <v>-0.9617</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1528</v>
+        <v>-0.5904</v>
       </c>
       <c r="O16" t="n">
-        <v>0.308</v>
+        <v>-0.3713</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6985</v>
+        <v>0.8098</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2592</v>
+        <v>0.7</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4393</v>
+        <v>0.1098</v>
       </c>
       <c r="V16" t="n">
-        <v>2.2862</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3333</v>
+        <v>1.0803</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4831</v>
+        <v>1.1293</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1498</v>
+        <v>-0.049</v>
       </c>
       <c r="G17" t="n">
         <v>0.7117</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3897</v>
+        <v>0.1366</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1261</v>
+        <v>0.2269</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7929</v>
+        <v>1.0288</v>
       </c>
       <c r="E18" t="n">
-        <v>0.122</v>
+        <v>0.3579</v>
       </c>
       <c r="F18" t="n">
         <v>0.671</v>
@@ -1858,10 +1858,10 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.228</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U18" t="n">
         <v>0.5895</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2383</v>
+        <v>-0.8865</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2562</v>
+        <v>-1.7401</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0178</v>
+        <v>0.8536</v>
       </c>
       <c r="G19" t="n">
-        <v>4.2946</v>
+        <v>-0.0522</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4346</v>
+        <v>-2.1234</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8601</v>
+        <v>2.0713</v>
       </c>
       <c r="J19" t="n">
-        <v>3.162</v>
+        <v>-0.8168</v>
       </c>
       <c r="K19" t="n">
-        <v>2.978</v>
+        <v>-2.4228</v>
       </c>
       <c r="L19" t="n">
-        <v>0.184</v>
+        <v>1.606</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1326</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4566</v>
+        <v>0.2993</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6761</v>
+        <v>0.4653</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.7988</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5004</v>
+        <v>-0.9761</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2388</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-1.0708</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
         <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6329</v>
+        <v>-0.9403</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.094</v>
+        <v>-2.0818</v>
       </c>
       <c r="F20" t="n">
-        <v>0.461</v>
+        <v>1.1415</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0522</v>
+        <v>4.2946</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1234</v>
+        <v>3.4346</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0713</v>
+        <v>0.8601</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8168</v>
+        <v>3.162</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4228</v>
+        <v>2.978</v>
       </c>
       <c r="L20" t="n">
-        <v>1.606</v>
+        <v>0.184</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7645999999999999</v>
+        <v>1.1326</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2993</v>
+        <v>0.4566</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4653</v>
+        <v>0.6761</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-5.7988</v>
       </c>
       <c r="R20" t="n">
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7225</v>
+        <v>-0.2016</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2592</v>
+        <v>0.4132</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4633</v>
+        <v>-0.6148</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>-0.3943</v>
       </c>
       <c r="W20" t="n">
         <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7368</v>
+        <v>-3.2992</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.758</v>
+        <v>-4.5221</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0212</v>
+        <v>1.2228</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9226</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9586</v>
+        <v>-0.521</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4358</v>
+        <v>-0.2341</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5946</v>
+        <v>-5.055</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8975</v>
+        <v>-4.1898</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6971000000000001</v>
+        <v>-0.8652</v>
       </c>
       <c r="G22" t="n">
         <v>-3.9846</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6822</v>
+        <v>-0.1426</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7468</v>
+        <v>-0.0391</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0646</v>
+        <v>-0.1034</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.224500000000001</v>
+        <v>7.0108</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5873999999999988</v>
+        <v>-0.5872999999999973</v>
       </c>
       <c r="F23" t="n">
-        <v>6.811800000000001</v>
+        <v>7.598000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>9.434199999999999</v>
+        <v>9.434200000000001</v>
       </c>
       <c r="H23" t="n">
         <v>1.3032</v>
@@ -2221,7 +2221,7 @@
         <v>8.1311</v>
       </c>
       <c r="J23" t="n">
-        <v>6.364000000000001</v>
+        <v>6.363999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>1.8644</v>
@@ -2230,10 +2230,10 @@
         <v>4.499400000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>3.0702</v>
+        <v>3.070199999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5612999999999999</v>
+        <v>-0.5613000000000001</v>
       </c>
       <c r="O23" t="n">
         <v>3.6316</v>
@@ -2248,19 +2248,19 @@
         <v>6.958899999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.8906</v>
+        <v>-2.1043</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3516</v>
+        <v>-0.3514</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.5391</v>
+        <v>-1.7528</v>
       </c>
       <c r="V23" t="n">
         <v>4.3199</v>
       </c>
       <c r="W23" t="n">
-        <v>4.9978</v>
+        <v>4.997800000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-0.6779000000000001</v>
